--- a/Bao cao/TCB/TCB_Model_2026_07_04.xlsx
+++ b/Bao cao/TCB/TCB_Model_2026_07_04.xlsx
@@ -41,7 +41,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +90,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -179,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +208,7 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -211,11 +218,11 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,9 +233,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="1" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -11679,30 +11686,30 @@
           <t>NIM (%)</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>0.0513</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>0.0532</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>0.0404</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>0.0426</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>0.0378</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="17">
         <f>'02_Assumptions'!G6</f>
         <v/>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="17">
         <f>'02_Assumptions'!H6</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="17">
         <f>'02_Assumptions'!I6</f>
         <v/>
       </c>
@@ -11752,30 +11759,30 @@
           <t>ROE (%)</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>0.1979</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>0.198</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>0.1485</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>0.1557</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>0.1585</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="17">
         <f>'04_PnL'!G5/AVERAGE('05_Balance_Sheet'!F10,'05_Balance_Sheet'!G10)</f>
         <v/>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="17">
         <f>'04_PnL'!H5/AVERAGE('05_Balance_Sheet'!G10,'05_Balance_Sheet'!H10)</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="17">
         <f>'04_PnL'!I5/AVERAGE('05_Balance_Sheet'!H10,'05_Balance_Sheet'!I10)</f>
         <v/>
       </c>
@@ -11786,30 +11793,30 @@
           <t>ROA (%)</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>0.0324</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>0.0292</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>0.0214</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>0.0222</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>0.0218</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="17">
         <f>'04_PnL'!G5/AVERAGE('05_Balance_Sheet'!F2,'05_Balance_Sheet'!G2)</f>
         <v/>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="17">
         <f>'04_PnL'!H5/AVERAGE('05_Balance_Sheet'!G2,'05_Balance_Sheet'!H2)</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="17">
         <f>'04_PnL'!I5/AVERAGE('05_Balance_Sheet'!H2,'05_Balance_Sheet'!I2)</f>
         <v/>
       </c>
@@ -11848,7 +11855,7 @@
         <f>'05_Balance_Sheet'!H11/'05_Balance_Sheet'!H12</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="17">
         <f>'05_Balance_Sheet'!I11/'05_Balance_Sheet'!I12</f>
         <v/>
       </c>
@@ -11961,19 +11968,19 @@
           <t>YOEA — Lợi suất TSSL (%)</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0.0683</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>0.0786</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.0828</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>0.0721</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>0.0674</v>
       </c>
       <c r="G10" s="14" t="n"/>
@@ -11986,19 +11993,19 @@
           <t>COF — Chi phí vốn (%)</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>0.0253</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>0.039</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.0623</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.0405</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>0.0396</v>
       </c>
       <c r="G11" s="14" t="n"/>
@@ -12066,7 +12073,7 @@
           <t>BV/share hiện tại (VND)</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>'05_Balance_Sheet'!F10*1000000000/'02_Assumptions'!$F$3</f>
         <v/>
       </c>
@@ -12077,7 +12084,7 @@
           <t>PV của RI 3 năm (VND)</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="20">
         <f>SUM(B31:D31)</f>
         <v/>
       </c>
@@ -12088,7 +12095,7 @@
           <t>PV của Continuing Value (VND)</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="20">
         <f>(D29*(1+B3)/(B2-B3))*D30</f>
         <v/>
       </c>
@@ -12117,7 +12124,7 @@
           <t>P/B hiện tại (x)</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>'02_Assumptions'!B2/B6</f>
         <v/>
       </c>
@@ -12128,11 +12135,11 @@
           <t>P/B hấp dẫn (x) — MUA</t>
         </is>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="22">
         <f t="array" ref="B13">MEDIAN(SMALL('13_PE_PB_History'!C2:C32, ROW(INDIRECT("1:"&amp;CEILING(COUNT('13_PE_PB_History'!C2:C32)/2,1)))))</f>
         <v/>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Median P/B nửa dưới (vùng mua hấp dẫn)</t>
         </is>
@@ -12144,11 +12151,11 @@
           <t>P/B median all-time (x) — FAIR VALUE</t>
         </is>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="21">
         <f>MEDIAN('13_PE_PB_History'!C2:C32)</f>
         <v/>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Median PB toàn bộ lịch sử</t>
         </is>
@@ -12160,11 +12167,11 @@
           <t>P/B Over (x) — BÁN / CHỐT LỜI</t>
         </is>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="25">
         <f t="array" ref="B15">MEDIAN(LARGE('13_PE_PB_History'!C2:C32, ROW(INDIRECT("1:"&amp;CEILING(COUNT('13_PE_PB_History'!C2:C32)/2,1)))))</f>
         <v/>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>Median P/B nửa trên (vùng chốt lời)</t>
         </is>
@@ -12176,7 +12183,7 @@
           <t>BV/share tương lai (2026F)</t>
         </is>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <f>B6+B26</f>
         <v/>
       </c>
@@ -12223,7 +12230,7 @@
           <t>Giá hiện tại (VND)</t>
         </is>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>'02_Assumptions'!B2</f>
         <v/>
       </c>
@@ -12252,15 +12259,15 @@
           <t>EPS (VND)</t>
         </is>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <f>'04_PnL'!G6</f>
         <v/>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>'04_PnL'!H6</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>'04_PnL'!I6</f>
         <v/>
       </c>
@@ -12271,15 +12278,15 @@
           <t>BVPS đầu kỳ (VND)</t>
         </is>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <f>B6</f>
         <v/>
       </c>
-      <c r="C27" s="19">
+      <c r="C27" s="20">
         <f>B27+B26</f>
         <v/>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>C27+C26</f>
         <v/>
       </c>
@@ -12290,15 +12297,15 @@
           <t>Capital Charge (VND)</t>
         </is>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="20">
         <f>B27*'07_Valuation'!$B$2</f>
         <v/>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>C27*'07_Valuation'!$B$2</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>D27*'07_Valuation'!$B$2</f>
         <v/>
       </c>
@@ -12309,15 +12316,15 @@
           <t>Residual Income (VND)</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <f>B26-B28</f>
         <v/>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="20">
         <f>C26-C28</f>
         <v/>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <f>D26-D28</f>
         <v/>
       </c>
@@ -12328,15 +12335,15 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <f>1/(1+'07_Valuation'!$B$2)^1</f>
         <v/>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <f>1/(1+'07_Valuation'!$B$2)^2</f>
         <v/>
       </c>
-      <c r="D30" s="26">
+      <c r="D30" s="27">
         <f>1/(1+'07_Valuation'!$B$2)^3</f>
         <v/>
       </c>
@@ -12347,15 +12354,15 @@
           <t>PV of RI</t>
         </is>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="20">
         <f>B29*B30</f>
         <v/>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <f>C29*C30</f>
         <v/>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="20">
         <f>D29*D30</f>
         <v/>
       </c>
@@ -12387,120 +12394,120 @@
           <t>COE \ g</t>
         </is>
       </c>
-      <c r="B2" s="27" t="n">
+      <c r="B2" s="28" t="n">
         <v>0.01</v>
       </c>
-      <c r="C2" s="27" t="n">
+      <c r="C2" s="28" t="n">
         <v>0.02</v>
       </c>
-      <c r="D2" s="27" t="n">
+      <c r="D2" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="E2" s="27" t="n">
+      <c r="E2" s="28" t="n">
         <v>0.04</v>
       </c>
-      <c r="F2" s="27" t="n">
+      <c r="F2" s="28" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="n">
+      <c r="A3" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="B3" s="19" t="n">
-        <v>38116.8833700943</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>40060.56232338537</v>
-      </c>
-      <c r="D3" s="19" t="n">
-        <v>42781.71285799285</v>
-      </c>
-      <c r="E3" s="19" t="n">
-        <v>46863.43865990409</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>53666.31499642282</v>
+      <c r="B3" s="20" t="n">
+        <v>37831.41106431252</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>39732.5006451902</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>42394.02605841895</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>46386.31417826208</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>53040.12771133397</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>35166.02655873129</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>36258.98454205297</v>
-      </c>
-      <c r="D4" s="19" t="n">
-        <v>37664.21623489514</v>
-      </c>
-      <c r="E4" s="19" t="n">
-        <v>39537.85849201803</v>
-      </c>
-      <c r="F4" s="19" t="n">
-        <v>42160.95765199008</v>
+      <c r="B4" s="20" t="n">
+        <v>34945.35339989405</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>36014.36278074461</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>37388.80341326675</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>39221.39092329628</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>41787.01343733762</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="29" t="n">
         <v>0.12</v>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>33292.18730384414</v>
-      </c>
-      <c r="C5" s="19" t="n">
-        <v>33982.25643872199</v>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>34825.67427023937</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>35879.94655963608</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>37235.43950314615</v>
+      <c r="B5" s="20" t="n">
+        <v>33112.70739428551</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>33787.65591918478</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>34612.59300517277</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>35643.76436265776</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>36969.55610799561</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>31998.06936273606</v>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>32467.73310299433</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>33022.79025057229</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>33688.85882766584</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>34502.94264411351</v>
+      <c r="B6" s="20" t="n">
+        <v>31847.07385315938</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>32306.44644738808</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>32849.34133147654</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>33500.8151923827</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>34297.06102237912</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="29" t="n">
         <v>0.16</v>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>31051.61577864765</v>
-      </c>
-      <c r="C7" s="29" t="n">
-        <v>31388.58176127528</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>31777.38866430716</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>32230.99671784436</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>32767.07896293377</v>
+      <c r="B7" s="20" t="n">
+        <v>30921.48098112662</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>31251.06345543336</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>31631.35092578729</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>32075.0196412002</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>32599.3553957791</v>
       </c>
     </row>
   </sheetData>
@@ -12890,35 +12897,35 @@
           <t>Thu nhập lãi thuần (NII)</t>
         </is>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="19">
         <f>'04_PnL'!B2</f>
         <v/>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="19">
         <f>'04_PnL'!C2</f>
         <v/>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="19">
         <f>'04_PnL'!D2</f>
         <v/>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="19">
         <f>'04_PnL'!E2</f>
         <v/>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="19">
         <f>'04_PnL'!F2</f>
         <v/>
       </c>
-      <c r="G2" s="18">
+      <c r="G2" s="19">
         <f>'04_PnL'!G2</f>
         <v/>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="19">
         <f>'04_PnL'!H2</f>
         <v/>
       </c>
-      <c r="I2" s="18">
+      <c r="I2" s="19">
         <f>'04_PnL'!I2</f>
         <v/>
       </c>
@@ -12929,35 +12936,35 @@
           <t>Tổng thu nhập HĐ (TOI)</t>
         </is>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="19">
         <f>'04_PnL'!B3</f>
         <v/>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="19">
         <f>'04_PnL'!C3</f>
         <v/>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="19">
         <f>'04_PnL'!D3</f>
         <v/>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="19">
         <f>'04_PnL'!E3</f>
         <v/>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="19">
         <f>'04_PnL'!F3</f>
         <v/>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="19">
         <f>'04_PnL'!G3</f>
         <v/>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="19">
         <f>'04_PnL'!H3</f>
         <v/>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="19">
         <f>'04_PnL'!I3</f>
         <v/>
       </c>
@@ -12968,35 +12975,35 @@
           <t>LN trước dự phòng (PPOP)</t>
         </is>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="19">
         <f>'04_PnL'!B4</f>
         <v/>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <f>'04_PnL'!C4</f>
         <v/>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="19">
         <f>'04_PnL'!D4</f>
         <v/>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="19">
         <f>'04_PnL'!E4</f>
         <v/>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="19">
         <f>'04_PnL'!F4</f>
         <v/>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="19">
         <f>'04_PnL'!G4</f>
         <v/>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="19">
         <f>'04_PnL'!H4</f>
         <v/>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="19">
         <f>'04_PnL'!I4</f>
         <v/>
       </c>
@@ -13007,35 +13014,35 @@
           <t>LNST (NPAT)</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="19">
         <f>'04_PnL'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>'04_PnL'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="19">
         <f>'04_PnL'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="19">
         <f>'04_PnL'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="19">
         <f>'04_PnL'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="19">
         <f>'04_PnL'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <f>'04_PnL'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <f>'04_PnL'!I5</f>
         <v/>
       </c>
@@ -13046,35 +13053,35 @@
           <t>EPS (VND)</t>
         </is>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>'04_PnL'!B6</f>
         <v/>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>'04_PnL'!C6</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>'04_PnL'!D6</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>'04_PnL'!E6</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>'04_PnL'!F6</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>'04_PnL'!G6</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f>'04_PnL'!H6</f>
         <v/>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <f>'04_PnL'!I6</f>
         <v/>
       </c>
@@ -13085,35 +13092,35 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="19">
         <f>'05_Balance_Sheet'!B2</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>'05_Balance_Sheet'!C2</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="19">
         <f>'05_Balance_Sheet'!D2</f>
         <v/>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="19">
         <f>'05_Balance_Sheet'!E2</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="19">
         <f>'05_Balance_Sheet'!F2</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="19">
         <f>'05_Balance_Sheet'!G2</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="19">
         <f>'05_Balance_Sheet'!H2</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="19">
         <f>'05_Balance_Sheet'!I2</f>
         <v/>
       </c>
@@ -13124,35 +13131,35 @@
           <t>Cho vay khách hàng (Gross)</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="19">
         <f>'05_Balance_Sheet'!B3</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>'05_Balance_Sheet'!C3</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="19">
         <f>'05_Balance_Sheet'!D3</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="19">
         <f>'05_Balance_Sheet'!E3</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="19">
         <f>'05_Balance_Sheet'!F3</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="19">
         <f>'05_Balance_Sheet'!G3</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="19">
         <f>'05_Balance_Sheet'!H3</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="19">
         <f>'05_Balance_Sheet'!I3</f>
         <v/>
       </c>
@@ -13163,35 +13170,35 @@
           <t>Trái phiếu doanh nghiệp</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="19">
         <f>'05_Balance_Sheet'!B4</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>'05_Balance_Sheet'!C4</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="19">
         <f>'05_Balance_Sheet'!D4</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="19">
         <f>'05_Balance_Sheet'!E4</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="19">
         <f>'05_Balance_Sheet'!F4</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="19">
         <f>'05_Balance_Sheet'!G4</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="19">
         <f>'05_Balance_Sheet'!H4</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="19">
         <f>'05_Balance_Sheet'!I4</f>
         <v/>
       </c>
@@ -13202,35 +13209,35 @@
           <t>Tiền gửi khách hàng</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="19">
         <f>'05_Balance_Sheet'!B5</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>'05_Balance_Sheet'!C5</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="19">
         <f>'05_Balance_Sheet'!D5</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="19">
         <f>'05_Balance_Sheet'!E5</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="19">
         <f>'05_Balance_Sheet'!F5</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <f>'05_Balance_Sheet'!G5</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="19">
         <f>'05_Balance_Sheet'!H5</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="19">
         <f>'05_Balance_Sheet'!I5</f>
         <v/>
       </c>
@@ -13241,35 +13248,35 @@
           <t>Giấy tờ có giá (Bonds)</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="19">
         <f>'05_Balance_Sheet'!B6</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>'05_Balance_Sheet'!C6</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="19">
         <f>'05_Balance_Sheet'!D6</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="19">
         <f>'05_Balance_Sheet'!E6</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="19">
         <f>'05_Balance_Sheet'!F6</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="19">
         <f>'05_Balance_Sheet'!G6</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="19">
         <f>'05_Balance_Sheet'!H6</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="19">
         <f>'05_Balance_Sheet'!I6</f>
         <v/>
       </c>
@@ -13280,35 +13287,35 @@
           <t>Tiền gửi Kho bạc NN</t>
         </is>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <f>'05_Balance_Sheet'!B7</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>'05_Balance_Sheet'!C7</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="19">
         <f>'05_Balance_Sheet'!D7</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="19">
         <f>'05_Balance_Sheet'!E7</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="19">
         <f>'05_Balance_Sheet'!F7</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="19">
         <f>'05_Balance_Sheet'!G7</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="19">
         <f>'05_Balance_Sheet'!H7</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="19">
         <f>'05_Balance_Sheet'!I7</f>
         <v/>
       </c>
@@ -13319,35 +13326,35 @@
           <t>Tiền gửi ký quỹ (trừ đi)</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <f>'05_Balance_Sheet'!B8</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>'05_Balance_Sheet'!C8</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="19">
         <f>'05_Balance_Sheet'!D8</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="19">
         <f>'05_Balance_Sheet'!E8</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="19">
         <f>'05_Balance_Sheet'!F8</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="19">
         <f>'05_Balance_Sheet'!G8</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="19">
         <f>'05_Balance_Sheet'!H8</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="19">
         <f>'05_Balance_Sheet'!I8</f>
         <v/>
       </c>
@@ -13358,35 +13365,35 @@
           <t>Vốn chuyên dùng (trừ đi)</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <f>'05_Balance_Sheet'!B9</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <f>'05_Balance_Sheet'!C9</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="19">
         <f>'05_Balance_Sheet'!D9</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="19">
         <f>'05_Balance_Sheet'!E9</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="19">
         <f>'05_Balance_Sheet'!F9</f>
         <v/>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="19">
         <f>'05_Balance_Sheet'!G9</f>
         <v/>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="19">
         <f>'05_Balance_Sheet'!H9</f>
         <v/>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="19">
         <f>'05_Balance_Sheet'!I9</f>
         <v/>
       </c>
@@ -13397,35 +13404,35 @@
           <t>Vốn chủ sở hữu (VCSH)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <f>'05_Balance_Sheet'!B10</f>
         <v/>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <f>'05_Balance_Sheet'!C10</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="19">
         <f>'05_Balance_Sheet'!D10</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="19">
         <f>'05_Balance_Sheet'!E10</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="19">
         <f>'05_Balance_Sheet'!F10</f>
         <v/>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="19">
         <f>'05_Balance_Sheet'!G10</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="19">
         <f>'05_Balance_Sheet'!H10</f>
         <v/>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="19">
         <f>'05_Balance_Sheet'!I10</f>
         <v/>
       </c>
@@ -13484,10 +13491,10 @@
           <t>Q3/18</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>10.8486033885</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>2.0494710047</v>
       </c>
       <c r="D2" s="14" t="n"/>
@@ -13499,10 +13506,10 @@
           <t>Q4/18</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>10.206529667</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>1.8832315269</v>
       </c>
       <c r="D3" s="14" t="n"/>
@@ -13514,10 +13521,10 @@
           <t>Q1/19</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>10.0607684914</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>1.6464212149</v>
       </c>
       <c r="D4" s="14" t="n"/>
@@ -13529,10 +13536,10 @@
           <t>Q2/19</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>8.5457101092</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>1.3519337912</v>
       </c>
       <c r="D5" s="14" t="n"/>
@@ -13544,10 +13551,10 @@
           <t>Q3/19</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>9.4717886055</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>1.4846296787</v>
       </c>
       <c r="D6" s="14" t="n"/>
@@ -13559,10 +13566,10 @@
           <t>Q4/19</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>8.7821250597</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>1.3913662797</v>
       </c>
       <c r="D7" s="14" t="n"/>
@@ -13574,10 +13581,10 @@
           <t>Q1/20</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>5.9406023083</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>0.968766836</v>
       </c>
       <c r="D8" s="14" t="n"/>
@@ -13589,10 +13596,10 @@
           <t>Q2/20</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>6.5290253263</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>1.062294609</v>
       </c>
       <c r="D9" s="14" t="n"/>
@@ -13604,10 +13611,10 @@
           <t>Q3/20</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>7.5261695389</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>1.2188483813</v>
       </c>
       <c r="D10" s="14" t="n"/>
@@ -13619,10 +13626,10 @@
           <t>Q4/20</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>10.2860934157</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>1.6737236525</v>
       </c>
       <c r="D11" s="14" t="n"/>
@@ -13634,10 +13641,10 @@
           <t>Q1/21</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>11.2185517693</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1.8651941237</v>
       </c>
       <c r="D12" s="14" t="n"/>
@@ -13649,10 +13656,10 @@
           <t>Q2/21</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>13.1316545048</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>2.3877963955</v>
       </c>
       <c r="D13" s="14" t="n"/>
@@ -13664,10 +13671,10 @@
           <t>Q3/21</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>9.818664228499999</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1.9531524668</v>
       </c>
       <c r="D14" s="14" t="n"/>
@@ -13679,10 +13686,10 @@
           <t>Q4/21</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>8.8579073991</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>1.7365199257</v>
       </c>
       <c r="D15" s="14" t="n"/>
@@ -13694,10 +13701,10 @@
           <t>Q1/22</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>6.614888531</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1.297252187</v>
       </c>
       <c r="D16" s="14" t="n"/>
@@ -13709,10 +13716,10 @@
           <t>Q2/22</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>4.3885697734</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>0.8591419325</v>
       </c>
       <c r="D17" s="14" t="n"/>
@@ -13724,10 +13731,10 @@
           <t>Q3/22</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>4.6050342182</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>0.8981549631</v>
       </c>
       <c r="D18" s="14" t="n"/>
@@ -13739,10 +13746,10 @@
           <t>Q4/22</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <v>5.0385353485</v>
       </c>
-      <c r="C19" s="17" t="n">
+      <c r="C19" s="18" t="n">
         <v>0.9051804774</v>
       </c>
       <c r="D19" s="14" t="n"/>
@@ -13754,10 +13761,10 @@
           <t>Q1/23</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <v>5.8110753933</v>
       </c>
-      <c r="C20" s="17" t="n">
+      <c r="C20" s="18" t="n">
         <v>0.9531244902</v>
       </c>
       <c r="D20" s="14" t="n"/>
@@ -13769,10 +13776,10 @@
           <t>Q2/23</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <v>6.4222572428</v>
       </c>
-      <c r="C21" s="17" t="n">
+      <c r="C21" s="18" t="n">
         <v>0.9427913607</v>
       </c>
       <c r="D21" s="14" t="n"/>
@@ -13784,10 +13791,10 @@
           <t>Q3/23</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="18" t="n">
         <v>7.1247900953</v>
       </c>
-      <c r="C22" s="17" t="n">
+      <c r="C22" s="18" t="n">
         <v>0.9693953467999999</v>
       </c>
       <c r="D22" s="14" t="n"/>
@@ -13799,10 +13806,10 @@
           <t>Q4/23</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <v>9.2616863103</v>
       </c>
-      <c r="C23" s="17" t="n">
+      <c r="C23" s="18" t="n">
         <v>1.2814120995</v>
       </c>
       <c r="D23" s="14" t="n"/>
@@ -13814,10 +13821,10 @@
           <t>Q1/24</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="18" t="n">
         <v>8.1382371231</v>
       </c>
-      <c r="C24" s="17" t="n">
+      <c r="C24" s="18" t="n">
         <v>1.1767518385</v>
       </c>
       <c r="D24" s="14" t="n"/>
@@ -13829,10 +13836,10 @@
           <t>Q2/24</t>
         </is>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="18" t="n">
         <v>7.9891802171</v>
       </c>
-      <c r="C25" s="17" t="n">
+      <c r="C25" s="18" t="n">
         <v>1.2506132202</v>
       </c>
       <c r="D25" s="14" t="n"/>
@@ -13844,10 +13851,10 @@
           <t>Q3/24</t>
         </is>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="18" t="n">
         <v>7.3616543745</v>
       </c>
-      <c r="C26" s="17" t="n">
+      <c r="C26" s="18" t="n">
         <v>1.1648980259</v>
       </c>
       <c r="D26" s="14" t="n"/>
@@ -13859,10 +13866,10 @@
           <t>Q4/24</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <v>8.512548075</v>
       </c>
-      <c r="C27" s="17" t="n">
+      <c r="C27" s="18" t="n">
         <v>1.2631495845</v>
       </c>
       <c r="D27" s="14" t="n"/>
@@ -13874,10 +13881,10 @@
           <t>Q1/25</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="18" t="n">
         <v>11.6477870099</v>
       </c>
-      <c r="C28" s="17" t="n">
+      <c r="C28" s="18" t="n">
         <v>1.6382492399</v>
       </c>
       <c r="D28" s="14" t="n"/>
@@ -13889,10 +13896,10 @@
           <t>Q2/25</t>
         </is>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="18" t="n">
         <v>13.5226658764</v>
       </c>
-      <c r="C29" s="17" t="n">
+      <c r="C29" s="18" t="n">
         <v>1.831859987</v>
       </c>
       <c r="D29" s="14" t="n"/>
@@ -13904,10 +13911,10 @@
           <t>Q3/25</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="18" t="n">
         <v>11.7340730437</v>
       </c>
-      <c r="C30" s="17" t="n">
+      <c r="C30" s="18" t="n">
         <v>1.574749298</v>
       </c>
       <c r="D30" s="14" t="n"/>
@@ -13919,10 +13926,10 @@
           <t>Q4/25</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="18" t="n">
         <v>8.9041391191</v>
       </c>
-      <c r="C31" s="17" t="n">
+      <c r="C31" s="18" t="n">
         <v>1.327280517</v>
       </c>
       <c r="D31" s="14" t="n"/>
@@ -13934,29 +13941,29 @@
           <t>Q1/26</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="18" t="n">
         <v>9.1391663895</v>
       </c>
-      <c r="C32" s="17" t="n">
+      <c r="C32" s="18" t="n">
         <v>1.345978018</v>
       </c>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="14" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>MEDIAN ALL-TIME</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <v>8.7821250597</v>
       </c>
-      <c r="C34" s="32" t="n">
+      <c r="C34" s="33" t="n">
         <v>1.327280517</v>
       </c>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
+      <c r="D34" s="34" t="n"/>
+      <c r="E34" s="34" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14007,409 +14014,409 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>Q4/21</t>
         </is>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="35">
         <f>'05_Balance_Sheet_Quarterly'!B5+'05_Balance_Sheet_Quarterly'!B9</f>
         <v/>
       </c>
-      <c r="C2" s="34">
+      <c r="C2" s="35">
         <f>'05_Balance_Sheet_Quarterly'!B7+'05_Balance_Sheet_Quarterly'!B10+'05_Balance_Sheet_Quarterly'!B11*0.0-'05_Balance_Sheet_Quarterly'!B12-'05_Balance_Sheet_Quarterly'!B13</f>
         <v/>
       </c>
-      <c r="D2" s="33" t="n"/>
-      <c r="E2" s="33" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>Q1/22</t>
         </is>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="35">
         <f>'05_Balance_Sheet_Quarterly'!C5+'05_Balance_Sheet_Quarterly'!C9</f>
         <v/>
       </c>
-      <c r="C3" s="34">
+      <c r="C3" s="35">
         <f>'05_Balance_Sheet_Quarterly'!C7+'05_Balance_Sheet_Quarterly'!C10+'05_Balance_Sheet_Quarterly'!C11*0.0-'05_Balance_Sheet_Quarterly'!C12-'05_Balance_Sheet_Quarterly'!C13</f>
         <v/>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="36">
         <f>(B3-B2)/B2</f>
         <v/>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="36">
         <f>(C3-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>Q2/22</t>
         </is>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="35">
         <f>'05_Balance_Sheet_Quarterly'!D5+'05_Balance_Sheet_Quarterly'!D9</f>
         <v/>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="35">
         <f>'05_Balance_Sheet_Quarterly'!D7+'05_Balance_Sheet_Quarterly'!D10+'05_Balance_Sheet_Quarterly'!D11*0.0-'05_Balance_Sheet_Quarterly'!D12-'05_Balance_Sheet_Quarterly'!D13</f>
         <v/>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <f>(B4-B2)/B2</f>
         <v/>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <f>(C4-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Q3/22</t>
         </is>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <f>'05_Balance_Sheet_Quarterly'!E5+'05_Balance_Sheet_Quarterly'!E9</f>
         <v/>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <f>'05_Balance_Sheet_Quarterly'!E7+'05_Balance_Sheet_Quarterly'!E10+'05_Balance_Sheet_Quarterly'!E11*0.0-'05_Balance_Sheet_Quarterly'!E12-'05_Balance_Sheet_Quarterly'!E13</f>
         <v/>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="36">
         <f>(B5-B2)/B2</f>
         <v/>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="36">
         <f>(C5-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Q4/22</t>
         </is>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="35">
         <f>'05_Balance_Sheet_Quarterly'!F5+'05_Balance_Sheet_Quarterly'!F9</f>
         <v/>
       </c>
-      <c r="C6" s="34">
+      <c r="C6" s="35">
         <f>'05_Balance_Sheet_Quarterly'!F7+'05_Balance_Sheet_Quarterly'!F10+'05_Balance_Sheet_Quarterly'!F11*0.0-'05_Balance_Sheet_Quarterly'!F12-'05_Balance_Sheet_Quarterly'!F13</f>
         <v/>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <f>(B6-B2)/B2</f>
         <v/>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="36">
         <f>(C6-C2)/C2</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>Q1/23</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="35">
         <f>'05_Balance_Sheet_Quarterly'!G5+'05_Balance_Sheet_Quarterly'!G9</f>
         <v/>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="35">
         <f>'05_Balance_Sheet_Quarterly'!G7+'05_Balance_Sheet_Quarterly'!G10+'05_Balance_Sheet_Quarterly'!G11*0.5-'05_Balance_Sheet_Quarterly'!G12-'05_Balance_Sheet_Quarterly'!G13</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="36">
         <f>(B7-B6)/B6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="36">
         <f>(C7-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>Q2/23</t>
         </is>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="35">
         <f>'05_Balance_Sheet_Quarterly'!H5+'05_Balance_Sheet_Quarterly'!H9</f>
         <v/>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="35">
         <f>'05_Balance_Sheet_Quarterly'!H7+'05_Balance_Sheet_Quarterly'!H10+'05_Balance_Sheet_Quarterly'!H11*0.5-'05_Balance_Sheet_Quarterly'!H12-'05_Balance_Sheet_Quarterly'!H13</f>
         <v/>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="36">
         <f>(B8-B6)/B6</f>
         <v/>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="36">
         <f>(C8-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Q3/23</t>
         </is>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>'05_Balance_Sheet_Quarterly'!I5+'05_Balance_Sheet_Quarterly'!I9</f>
         <v/>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>'05_Balance_Sheet_Quarterly'!I7+'05_Balance_Sheet_Quarterly'!I10+'05_Balance_Sheet_Quarterly'!I11*0.5-'05_Balance_Sheet_Quarterly'!I12-'05_Balance_Sheet_Quarterly'!I13</f>
         <v/>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <f>(B9-B6)/B6</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="36">
         <f>(C9-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>Q4/23</t>
         </is>
       </c>
-      <c r="B10" s="34">
+      <c r="B10" s="35">
         <f>'05_Balance_Sheet_Quarterly'!J5+'05_Balance_Sheet_Quarterly'!J9</f>
         <v/>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>'05_Balance_Sheet_Quarterly'!J7+'05_Balance_Sheet_Quarterly'!J10+'05_Balance_Sheet_Quarterly'!J11*0.5-'05_Balance_Sheet_Quarterly'!J12-'05_Balance_Sheet_Quarterly'!J13</f>
         <v/>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="36">
         <f>(B10-B6)/B6</f>
         <v/>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="36">
         <f>(C10-C6)/C6</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>Q1/24</t>
         </is>
       </c>
-      <c r="B11" s="34">
+      <c r="B11" s="35">
         <f>'05_Balance_Sheet_Quarterly'!K5+'05_Balance_Sheet_Quarterly'!K9</f>
         <v/>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="35">
         <f>'05_Balance_Sheet_Quarterly'!K7+'05_Balance_Sheet_Quarterly'!K10+'05_Balance_Sheet_Quarterly'!K11*0.4-'05_Balance_Sheet_Quarterly'!K12-'05_Balance_Sheet_Quarterly'!K13</f>
         <v/>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <f>(B11-B10)/B10</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>(C11-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Q2/24</t>
         </is>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="35">
         <f>'05_Balance_Sheet_Quarterly'!L5+'05_Balance_Sheet_Quarterly'!L9</f>
         <v/>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="35">
         <f>'05_Balance_Sheet_Quarterly'!L7+'05_Balance_Sheet_Quarterly'!L10+'05_Balance_Sheet_Quarterly'!L11*0.4-'05_Balance_Sheet_Quarterly'!L12-'05_Balance_Sheet_Quarterly'!L13</f>
         <v/>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <f>(B12-B10)/B10</f>
         <v/>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="36">
         <f>(C12-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>Q3/24</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="35">
         <f>'05_Balance_Sheet_Quarterly'!M5+'05_Balance_Sheet_Quarterly'!M9</f>
         <v/>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="35">
         <f>'05_Balance_Sheet_Quarterly'!M7+'05_Balance_Sheet_Quarterly'!M10+'05_Balance_Sheet_Quarterly'!M11*0.4-'05_Balance_Sheet_Quarterly'!M12-'05_Balance_Sheet_Quarterly'!M13</f>
         <v/>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="36">
         <f>(B13-B10)/B10</f>
         <v/>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="36">
         <f>(C13-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Q4/24</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'05_Balance_Sheet_Quarterly'!N5+'05_Balance_Sheet_Quarterly'!N9</f>
         <v/>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>'05_Balance_Sheet_Quarterly'!N7+'05_Balance_Sheet_Quarterly'!N10+'05_Balance_Sheet_Quarterly'!N11*0.4-'05_Balance_Sheet_Quarterly'!N12-'05_Balance_Sheet_Quarterly'!N13</f>
         <v/>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>(B14-B10)/B10</f>
         <v/>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>(C14-C10)/C10</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Q1/25</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>'05_Balance_Sheet_Quarterly'!O5+'05_Balance_Sheet_Quarterly'!O9</f>
         <v/>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>'05_Balance_Sheet_Quarterly'!O7+'05_Balance_Sheet_Quarterly'!O10+'05_Balance_Sheet_Quarterly'!O11*0.2-'05_Balance_Sheet_Quarterly'!O12-'05_Balance_Sheet_Quarterly'!O13</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>(B15-B14)/B14</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>(C15-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Q2/25</t>
         </is>
       </c>
-      <c r="B16" s="34">
+      <c r="B16" s="35">
         <f>'05_Balance_Sheet_Quarterly'!P5+'05_Balance_Sheet_Quarterly'!P9</f>
         <v/>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="35">
         <f>'05_Balance_Sheet_Quarterly'!P7+'05_Balance_Sheet_Quarterly'!P10+'05_Balance_Sheet_Quarterly'!P11*0.2-'05_Balance_Sheet_Quarterly'!P12-'05_Balance_Sheet_Quarterly'!P13</f>
         <v/>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="36">
         <f>(B16-B14)/B14</f>
         <v/>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="36">
         <f>(C16-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Q3/25</t>
         </is>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="35">
         <f>'05_Balance_Sheet_Quarterly'!Q5+'05_Balance_Sheet_Quarterly'!Q9</f>
         <v/>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="35">
         <f>'05_Balance_Sheet_Quarterly'!Q7+'05_Balance_Sheet_Quarterly'!Q10+'05_Balance_Sheet_Quarterly'!Q11*0.2-'05_Balance_Sheet_Quarterly'!Q12-'05_Balance_Sheet_Quarterly'!Q13</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="36">
         <f>(B17-B14)/B14</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="36">
         <f>(C17-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Q4/25</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>'05_Balance_Sheet_Quarterly'!R5+'05_Balance_Sheet_Quarterly'!R9</f>
         <v/>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <f>'05_Balance_Sheet_Quarterly'!R7+'05_Balance_Sheet_Quarterly'!R10+'05_Balance_Sheet_Quarterly'!R11*0.2-'05_Balance_Sheet_Quarterly'!R12-'05_Balance_Sheet_Quarterly'!R13</f>
         <v/>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="36">
         <f>(B18-B14)/B14</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="36">
         <f>(C18-C14)/C14</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Q1/26</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="35">
         <f>'05_Balance_Sheet_Quarterly'!S5+'05_Balance_Sheet_Quarterly'!S9</f>
         <v/>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="35">
         <f>'05_Balance_Sheet_Quarterly'!S7+'05_Balance_Sheet_Quarterly'!S10+'05_Balance_Sheet_Quarterly'!S11*0.2-'05_Balance_Sheet_Quarterly'!S12-'05_Balance_Sheet_Quarterly'!S13</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="36">
         <f>(B19-B18)/B18</f>
         <v/>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="36">
         <f>(C19-C18)/C18</f>
         <v/>
       </c>
@@ -14586,593 +14593,593 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Trung bình ngành</t>
         </is>
       </c>
-      <c r="B2" s="37" t="n">
+      <c r="B2" s="38" t="n">
         <v>2.385</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="38" t="n">
         <v>4.357222222222222</v>
       </c>
-      <c r="D2" s="37" t="n">
+      <c r="D2" s="38" t="n">
         <v>16.84888888888889</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="38" t="n">
         <v>15.58666666666667</v>
       </c>
-      <c r="F2" s="37" t="n">
+      <c r="F2" s="38" t="n">
         <v>33.94777777777777</v>
       </c>
-      <c r="G2" s="38" t="n">
+      <c r="G2" s="39" t="n">
         <v>1.454444444444444</v>
       </c>
-      <c r="H2" s="37" t="n">
+      <c r="H2" s="38" t="n">
         <v>3.509444444444445</v>
       </c>
-      <c r="I2" s="36" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>VCB — Vietcombank</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="36" t="n">
         <v>0.0063</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="36" t="n">
         <v>0.0409</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="36" t="n">
         <v>0.3255</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="36" t="n">
         <v>0.1617</v>
       </c>
-      <c r="F3" s="35" t="n">
+      <c r="F3" s="36" t="n">
         <v>0.325</v>
       </c>
-      <c r="G3" s="39" t="n">
+      <c r="G3" s="40" t="n">
         <v>2.21</v>
       </c>
-      <c r="H3" s="35" t="n">
+      <c r="H3" s="36" t="n">
         <v>0.0478</v>
       </c>
-      <c r="I3" s="34" t="n">
+      <c r="I3" s="35" t="n">
         <v>518051.855828</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>BID — BIDV</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="36" t="n">
         <v>0.0178</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="36" t="n">
         <v>0.0263</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="36" t="n">
         <v>0.1949</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="36" t="n">
         <v>0.1443</v>
       </c>
-      <c r="F4" s="35" t="n">
+      <c r="F4" s="36" t="n">
         <v>0.3202</v>
       </c>
-      <c r="G4" s="39" t="n">
+      <c r="G4" s="40" t="n">
         <v>1.61</v>
       </c>
-      <c r="H4" s="35" t="n">
+      <c r="H4" s="36" t="n">
         <v>0.0233</v>
       </c>
-      <c r="I4" s="34" t="n">
+      <c r="I4" s="35" t="n">
         <v>307582.7551225</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>CTG — VietinBank</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="36" t="n">
         <v>0.0103</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="36" t="n">
         <v>0.0389</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="36" t="n">
         <v>0.2408</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="36" t="n">
         <v>0.1899</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="36" t="n">
         <v>0.2494</v>
       </c>
-      <c r="G5" s="39" t="n">
+      <c r="G5" s="40" t="n">
         <v>1.41</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="36" t="n">
         <v>0.0187</v>
       </c>
-      <c r="I5" s="34" t="n">
+      <c r="I5" s="35" t="n">
         <v>265241.15935355</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>TCB — Techcombank</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="42" t="n">
         <v>0.0111</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="42" t="n">
         <v>0.04849999999999999</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="42" t="n">
         <v>0.3145</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="42" t="n">
         <v>0.1489</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="42" t="n">
         <v>0.2829</v>
       </c>
-      <c r="G6" s="42" t="n">
+      <c r="G6" s="43" t="n">
         <v>1.28</v>
       </c>
-      <c r="H6" s="41" t="n">
+      <c r="H6" s="42" t="n">
         <v>0.03759999999999999</v>
       </c>
-      <c r="I6" s="43" t="n">
+      <c r="I6" s="44" t="n">
         <v>238097.6779104</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>MBB — MBBank</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="36" t="n">
         <v>0.0144</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>0.0539</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="36" t="n">
         <v>0.3227</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="36" t="n">
         <v>0.2058</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="36" t="n">
         <v>0.2494</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="40" t="n">
         <v>1.38</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="36" t="n">
         <v>0.0327</v>
       </c>
-      <c r="I7" s="34" t="n">
+      <c r="I7" s="35" t="n">
         <v>206207.9976704</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>ACB — ACB</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <v>0.0098</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="36" t="n">
         <v>0.0399</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="36" t="n">
         <v>0.2123</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="36" t="n">
         <v>0.175</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="36" t="n">
         <v>0.3201</v>
       </c>
-      <c r="G8" s="39" t="n">
+      <c r="G8" s="40" t="n">
         <v>1.33</v>
       </c>
-      <c r="H8" s="35" t="n">
+      <c r="H8" s="36" t="n">
         <v>0.0325</v>
       </c>
-      <c r="I8" s="34" t="n">
+      <c r="I8" s="35" t="n">
         <v>131470.15732605</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>VIB — VIB</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="36" t="n">
         <v>0.0298</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="36" t="n">
         <v>0.0424</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="36" t="n">
         <v>0.1393</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="36" t="n">
         <v>0.1824</v>
       </c>
-      <c r="F9" s="35" t="n">
+      <c r="F9" s="36" t="n">
         <v>0.3161</v>
       </c>
-      <c r="G9" s="39" t="n">
+      <c r="G9" s="40" t="n">
         <v>1.14</v>
       </c>
-      <c r="H9" s="35" t="n">
+      <c r="H9" s="36" t="n">
         <v>0.0113</v>
       </c>
-      <c r="I9" s="34" t="n">
+      <c r="I9" s="35" t="n">
         <v>55995.8939295</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>HDB — HDBank</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="36" t="n">
         <v>0.0264</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="36" t="n">
         <v>0.0572</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="36" t="n">
         <v>0.1021</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="36" t="n">
         <v>0.2357</v>
       </c>
-      <c r="F10" s="35" t="n">
+      <c r="F10" s="36" t="n">
         <v>0.2599</v>
       </c>
-      <c r="G10" s="39" t="n">
+      <c r="G10" s="40" t="n">
         <v>1.62</v>
       </c>
-      <c r="H10" s="35" t="n">
+      <c r="H10" s="36" t="n">
         <v>0.1006</v>
       </c>
-      <c r="I10" s="34" t="n">
+      <c r="I10" s="35" t="n">
         <v>134892.19690485</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>STB — Sacombank</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="36" t="n">
         <v>0.06860000000000001</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="36" t="n">
         <v>0.04</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="36" t="n">
         <v>0.1592</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="36" t="n">
         <v>0.1031</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F11" s="36" t="n">
         <v>0.4521</v>
       </c>
-      <c r="G11" s="39" t="n">
+      <c r="G11" s="40" t="n">
         <v>2.21</v>
       </c>
-      <c r="H11" s="35" t="n">
+      <c r="H11" s="36" t="n">
         <v>-0.0024</v>
       </c>
-      <c r="I11" s="34" t="n">
+      <c r="I11" s="35" t="n">
         <v>135735.531552</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>VPB — VPBank</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="36" t="n">
         <v>0.0365</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="36" t="n">
         <v>0.0664</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="36" t="n">
         <v>0.1309</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="36" t="n">
         <v>0.1357</v>
       </c>
-      <c r="F12" s="35" t="n">
+      <c r="F12" s="36" t="n">
         <v>0.2169</v>
       </c>
-      <c r="G12" s="39" t="n">
+      <c r="G12" s="40" t="n">
         <v>1.18</v>
       </c>
-      <c r="H12" s="35" t="n">
+      <c r="H12" s="36" t="n">
         <v>0.1023</v>
       </c>
-      <c r="I12" s="34" t="n">
+      <c r="I12" s="35" t="n">
         <v>220563.0761078</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>TPB — TPBank</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="36" t="n">
         <v>0.0219</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="36" t="n">
         <v>0.0443</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="36" t="n">
         <v>0.1745</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="36" t="n">
         <v>0.1401</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="36" t="n">
         <v>0.4585</v>
       </c>
-      <c r="G13" s="39" t="n">
+      <c r="G13" s="40" t="n">
         <v>0.96</v>
       </c>
-      <c r="H13" s="35" t="n">
+      <c r="H13" s="36" t="n">
         <v>0.0326</v>
       </c>
-      <c r="I13" s="34" t="n">
+      <c r="I13" s="35" t="n">
         <v>45910.47574815</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>MSB — MSB</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="36" t="n">
         <v>0.027</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="36" t="n">
         <v>0.0604</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="36" t="n">
         <v>0.2551</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="36" t="n">
         <v>0.1377</v>
       </c>
-      <c r="F14" s="35" t="n">
+      <c r="F14" s="36" t="n">
         <v>0.3451</v>
       </c>
-      <c r="G14" s="39" t="n">
+      <c r="G14" s="40" t="n">
         <v>1.14</v>
       </c>
-      <c r="H14" s="35" t="n">
+      <c r="H14" s="36" t="n">
         <v>0.0464</v>
       </c>
-      <c r="I14" s="34" t="n">
+      <c r="I14" s="35" t="n">
         <v>49920</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>EIB — Eximbank</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="36" t="n">
         <v>0.031</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="36" t="n">
         <v>0.0295</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="36" t="n">
         <v>0.1337</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="36" t="n">
         <v>0.0407</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="36" t="n">
         <v>0.5698</v>
       </c>
-      <c r="G15" s="39" t="n">
+      <c r="G15" s="40" t="n">
         <v>1.46</v>
       </c>
-      <c r="H15" s="35" t="n">
+      <c r="H15" s="36" t="n">
         <v>0.0289</v>
       </c>
-      <c r="I15" s="34" t="n">
+      <c r="I15" s="35" t="n">
         <v>38465.18053455</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>LPB — LienVietPostBank</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="36" t="n">
         <v>0.0186</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="36" t="n">
         <v>0.039</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="36" t="n">
         <v>0.0649</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.1843</v>
       </c>
-      <c r="F16" s="35" t="n">
+      <c r="F16" s="36" t="n">
         <v>0.3014</v>
       </c>
-      <c r="G16" s="39" t="n">
+      <c r="G16" s="40" t="n">
         <v>3.08</v>
       </c>
-      <c r="H16" s="35" t="n">
+      <c r="H16" s="36" t="n">
         <v>0.0284</v>
       </c>
-      <c r="I16" s="34" t="n">
+      <c r="I16" s="35" t="n">
         <v>152351.3871</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>SHB — SHB</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="36" t="n">
         <v>0.0265</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="36" t="n">
         <v>0.0357</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="36" t="n">
         <v>0.0663</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.2078</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="36" t="n">
         <v>0.1717</v>
       </c>
-      <c r="G17" s="39" t="n">
+      <c r="G17" s="40" t="n">
         <v>1.02</v>
       </c>
-      <c r="H17" s="35" t="n">
+      <c r="H17" s="36" t="n">
         <v>0.0201</v>
       </c>
-      <c r="I17" s="34" t="n">
+      <c r="I17" s="35" t="n">
         <v>72941.55738870001</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>OCB — OCB</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="36" t="n">
         <v>0.0359</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="36" t="n">
         <v>0.0475</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="36" t="n">
         <v>0.1067</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="36" t="n">
         <v>0.1118</v>
       </c>
-      <c r="F18" s="35" t="n">
+      <c r="F18" s="36" t="n">
         <v>0.3709</v>
       </c>
-      <c r="G18" s="39" t="n">
+      <c r="G18" s="40" t="n">
         <v>1.01</v>
       </c>
-      <c r="H18" s="35" t="n">
+      <c r="H18" s="36" t="n">
         <v>0.0272</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="I18" s="35" t="n">
         <v>35218.866449</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>BAB — BacABank</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="36" t="n">
         <v>0.0191</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="36" t="n">
         <v>0.0319</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="36" t="n">
         <v>0.0305</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="36" t="n">
         <v>0.0882</v>
       </c>
-      <c r="F19" s="35" t="n">
+      <c r="F19" s="36" t="n">
         <v>0.5122</v>
       </c>
-      <c r="G19" s="39" t="n">
+      <c r="G19" s="40" t="n">
         <v>0.99</v>
       </c>
-      <c r="H19" s="35" t="n">
+      <c r="H19" s="36" t="n">
         <v>0.0246</v>
       </c>
-      <c r="I19" s="34" t="n">
+      <c r="I19" s="35" t="n">
         <v>13484.8433772</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>NAB — NamABank</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="36" t="n">
         <v>0.0183</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="36" t="n">
         <v>0.0416</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="36" t="n">
         <v>0.05889999999999999</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="36" t="n">
         <v>0.2125</v>
       </c>
-      <c r="F20" s="35" t="n">
+      <c r="F20" s="36" t="n">
         <v>0.389</v>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="40" t="n">
         <v>1.15</v>
       </c>
-      <c r="H20" s="35" t="n">
+      <c r="H20" s="36" t="n">
         <v>0.0191</v>
       </c>
-      <c r="I20" s="34" t="n">
+      <c r="I20" s="35" t="n">
         <v>28280.5718942</v>
       </c>
     </row>
@@ -15207,7 +15214,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Ngày lập: 04/07/2026 08:38</t>
+          <t>Ngày lập: 04/07/2026 11:00</t>
         </is>
       </c>
     </row>
@@ -15266,8 +15273,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
@@ -15460,13 +15470,18 @@
         <v/>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0364</v>
+        <v>0.0362</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Năm 1 (2026E) cơ học (YOEA/COF): YOEA=6.64% (gốc 6.74% x hệ số 0.985), COF=3.84% (gốc 3.96% x hệ số 0.97) → NIM cơ học=3.80%. Đã có Q1 thực tế = 3.44% → NIM năm 1 = 50% cơ học + 50% Q1 thực tế = 3.62%. Năm 2/3 GIỮ NGUYÊN bằng năm 1 (không giả định NIM tăng, để định giá an toàn hơn).</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -15628,13 +15643,13 @@
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
       <c r="F11" s="14" t="n"/>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="I11" s="16" t="n">
+      <c r="I11" s="17" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -15649,13 +15664,13 @@
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="n"/>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>0.140492</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <v>0.140492</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="17" t="n">
         <v>0.140492</v>
       </c>
     </row>
@@ -15672,7 +15687,7 @@
       <c r="F13" s="14" t="n"/>
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="14" t="n"/>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="17" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -15687,13 +15702,13 @@
       <c r="D14" s="14" t="n"/>
       <c r="E14" s="14" t="n"/>
       <c r="F14" s="14" t="n"/>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="I14" s="16" t="n">
+      <c r="I14" s="17" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -15708,13 +15723,13 @@
       <c r="D15" s="14" t="n"/>
       <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="n"/>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>1.6600724337</v>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="18" t="n">
         <v>1.6600724337</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="18" t="n">
         <v>1.6600724337</v>
       </c>
     </row>
@@ -15813,7 +15828,7 @@
           <t>IEA_end gốc (2025A)</t>
         </is>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="19">
         <f>'05_Balance_Sheet'!F2</f>
         <v/>
       </c>
@@ -15824,7 +15839,7 @@
           <t>DepBonds gốc (2025A)</t>
         </is>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <f>SUM('05_Balance_Sheet'!F5:F6)</f>
         <v/>
       </c>
@@ -16027,30 +16042,30 @@
           <t>IEA bình quân (tỷ)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>520194.099</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>569081.67</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>685155.2325</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>833463.7640000001</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>1009356.682</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="18">
         <f>(F18+G18)/2</f>
         <v/>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="18">
         <f>(G18+H18)/2</f>
         <v/>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="18">
         <f>(H18+I18)/2</f>
         <v/>
       </c>
@@ -16097,29 +16112,29 @@
           <t>NIM (%)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>0.0513</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>0.0532</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>0.0404</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>0.0426</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>0.0378</v>
       </c>
-      <c r="G4" s="17" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="H4" s="17" t="n">
-        <v>0.0364</v>
-      </c>
-      <c r="I4" s="17" t="n">
-        <v>0.0364</v>
+      <c r="G4" s="18" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>0.0362</v>
       </c>
     </row>
     <row r="5">
@@ -16128,30 +16143,30 @@
           <t>NII (tỷ)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>26698.613</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>30289.775</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>27691.12</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>35507.963</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>38155.091</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>G2*'02_Assumptions'!G6</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>H2*'02_Assumptions'!H6</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>I2*'02_Assumptions'!I6</f>
         <v/>
       </c>
@@ -16162,19 +16177,19 @@
           <t>Thu nhập dịch vụ</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>6382.24</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>8152.605</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>8714.897000000001</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>8042.248</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>8771.995000000001</v>
       </c>
       <c r="G6" s="14" t="n"/>
@@ -16187,19 +16202,19 @@
           <t>Thu nhập ngoại hối</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>231.416</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>-275.063</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>195.75</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>592.556</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>1642.201</v>
       </c>
       <c r="G7" s="14" t="n"/>
@@ -16212,19 +16227,19 @@
           <t>Thu nhập CK đầu tư</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>1956.713</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>183.708</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>990.453</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>2440.358</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>2898.295</v>
       </c>
       <c r="G8" s="14" t="n"/>
@@ -16237,19 +16252,19 @@
           <t>Thu nhập khác</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>1803.246</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>2167.375</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>2434.116</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>342.711</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>1884.342</v>
       </c>
       <c r="G9" s="14" t="n"/>
@@ -16262,28 +16277,28 @@
           <t>Tổng thu nhập ngoài lãi</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>10377.678</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>10237.416</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>12369.972</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>11482.43399999999</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>15236.034</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>17521.4391</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>20149.654965</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>22970.6066601</v>
       </c>
     </row>
@@ -16293,30 +16308,30 @@
           <t>Tổng thu nhập HĐ - TOI</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>37076.291</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>40527.191</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>40061.092</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>46990.397</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>53391.125</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>G5+G10</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="18">
         <f>H5+H10</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="18">
         <f>I5+I10</f>
         <v/>
       </c>
@@ -16327,19 +16342,19 @@
           <t>NII/TOI (%)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>72.01000000000001</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>74.73999999999999</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>69.12</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>75.56</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>71.45999999999999</v>
       </c>
       <c r="G12" s="14" t="n"/>
@@ -16352,30 +16367,30 @@
           <t>Chi phí HĐ - OPEX</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>11173.395</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>13023.129</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>13251.796</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>15369.735</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>16432.434</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="18">
         <f>G11*'02_Assumptions'!G7</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="18">
         <f>H11*'02_Assumptions'!H7</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>I11*'02_Assumptions'!I7</f>
         <v/>
       </c>
@@ -16386,30 +16401,30 @@
           <t>PPOP - LN trước dự phòng</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>25902.896</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>27504.062</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>26809.296</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>31620.662</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>36958.691</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="18">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="18">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="18">
         <f>I11-I13</f>
         <v/>
       </c>
@@ -16420,19 +16435,19 @@
           <t>PPOP/TOI (%)</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <v>69.86</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>67.87</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>66.92</v>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>67.29000000000001</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <v>69.22</v>
       </c>
       <c r="G15" s="14" t="n"/>
@@ -16445,30 +16460,30 @@
           <t>Dự phòng tín dụng</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <v>2664.603</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1936.294</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>3921.068</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>4082.294</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="18" t="n">
         <v>4420.625</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="18">
         <f>(('05_Balance_Sheet'!F3+'05_Balance_Sheet'!G3)/2)*'02_Assumptions'!G8</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="18">
         <f>(('05_Balance_Sheet'!G3+'05_Balance_Sheet'!H3)/2)*'02_Assumptions'!H8</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="18">
         <f>(('05_Balance_Sheet'!H3+'05_Balance_Sheet'!I3)/2)*'02_Assumptions'!I8</f>
         <v/>
       </c>
@@ -16479,30 +16494,30 @@
           <t>LN trước thuế - PBT</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>23238.293</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>25567.768</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>22888.228</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>27538.368</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>32538.066</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="18">
         <f>G14-G16</f>
         <v/>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="18">
         <f>H14-H16</f>
         <v/>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="18">
         <f>I14-I16</f>
         <v/>
       </c>
@@ -16513,30 +16528,30 @@
           <t>IEA cuối kỳ (tỷ)</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <v>520194.1</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="18" t="n">
         <v>617969.2</v>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <v>752341.2</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="18" t="n">
         <v>914586.3</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="18" t="n">
         <v>1104127.1</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="18">
         <f>F18*(1+G3)</f>
         <v/>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="18">
         <f>G18*(1+H3)</f>
         <v/>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="18">
         <f>H18*(1+I3)</f>
         <v/>
       </c>
@@ -16658,58 +16673,58 @@
           <t>Thu nhập lãi thuần - NII</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>7244.603</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>8111.063</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>7793.84</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>7565.461</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>6819.411</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="18" t="n">
         <v>6526.88</v>
       </c>
-      <c r="H2" s="17" t="n">
+      <c r="H2" s="18" t="n">
         <v>6294.877</v>
       </c>
-      <c r="I2" s="17" t="n">
+      <c r="I2" s="18" t="n">
         <v>7272.16</v>
       </c>
-      <c r="J2" s="17" t="n">
+      <c r="J2" s="18" t="n">
         <v>7597.203</v>
       </c>
-      <c r="K2" s="17" t="n">
+      <c r="K2" s="18" t="n">
         <v>8499.544</v>
       </c>
-      <c r="L2" s="17" t="n">
+      <c r="L2" s="18" t="n">
         <v>9477.925999999999</v>
       </c>
-      <c r="M2" s="17" t="n">
+      <c r="M2" s="18" t="n">
         <v>8928.675999999999</v>
       </c>
-      <c r="N2" s="17" t="n">
+      <c r="N2" s="18" t="n">
         <v>8601.816999999999</v>
       </c>
-      <c r="O2" s="17" t="n">
+      <c r="O2" s="18" t="n">
         <v>8305.393</v>
       </c>
-      <c r="P2" s="17" t="n">
+      <c r="P2" s="18" t="n">
         <v>9137.075999999999</v>
       </c>
-      <c r="Q2" s="17" t="n">
+      <c r="Q2" s="18" t="n">
         <v>9924.643</v>
       </c>
-      <c r="R2" s="17" t="n">
+      <c r="R2" s="18" t="n">
         <v>10787.979</v>
       </c>
-      <c r="S2" s="17" t="n">
+      <c r="S2" s="18" t="n">
         <v>9522.053</v>
       </c>
     </row>
@@ -16719,58 +16734,58 @@
           <t>Thu nhập ngoài lãi</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>2914.408</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>1895.317</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>3140.54</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>2772.907</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>2607.911</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="18" t="n">
         <v>2773.094</v>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="18" t="n">
         <v>3030.294</v>
       </c>
-      <c r="I3" s="17" t="n">
+      <c r="I3" s="18" t="n">
         <v>3146.333</v>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="18" t="n">
         <v>3420.251</v>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="K3" s="18" t="n">
         <v>3762.223</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="18" t="n">
         <v>3941.77</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="18" t="n">
         <v>2825.659</v>
       </c>
-      <c r="N3" s="17" t="n">
+      <c r="N3" s="18" t="n">
         <v>952.782</v>
       </c>
-      <c r="O3" s="17" t="n">
+      <c r="O3" s="18" t="n">
         <v>3305.805</v>
       </c>
-      <c r="P3" s="17" t="n">
+      <c r="P3" s="18" t="n">
         <v>3605.955</v>
       </c>
-      <c r="Q3" s="17" t="n">
+      <c r="Q3" s="18" t="n">
         <v>4317.48</v>
       </c>
-      <c r="R3" s="17" t="n">
+      <c r="R3" s="18" t="n">
         <v>4006.794</v>
       </c>
-      <c r="S3" s="17" t="n">
+      <c r="S3" s="18" t="n">
         <v>4152.221</v>
       </c>
     </row>
@@ -16780,58 +16795,58 @@
           <t>Tổng thu nhập HĐ - TOI</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>10159.011</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>10006.38</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>10934.38</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>10338.368</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>9427.322</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>9299.974</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>9325.171</v>
       </c>
-      <c r="I4" s="17" t="n">
+      <c r="I4" s="18" t="n">
         <v>10418.493</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="18" t="n">
         <v>11017.454</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="18" t="n">
         <v>12261.767</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="18" t="n">
         <v>13419.696</v>
       </c>
-      <c r="M4" s="17" t="n">
+      <c r="M4" s="18" t="n">
         <v>11754.335</v>
       </c>
-      <c r="N4" s="17" t="n">
+      <c r="N4" s="18" t="n">
         <v>9554.599</v>
       </c>
-      <c r="O4" s="17" t="n">
+      <c r="O4" s="18" t="n">
         <v>11611.198</v>
       </c>
-      <c r="P4" s="17" t="n">
+      <c r="P4" s="18" t="n">
         <v>12743.031</v>
       </c>
-      <c r="Q4" s="17" t="n">
+      <c r="Q4" s="18" t="n">
         <v>14242.123</v>
       </c>
-      <c r="R4" s="17" t="n">
+      <c r="R4" s="18" t="n">
         <v>14794.773</v>
       </c>
-      <c r="S4" s="17" t="n">
+      <c r="S4" s="18" t="n">
         <v>13674.274</v>
       </c>
     </row>
@@ -16841,58 +16856,58 @@
           <t>Chi phí hoạt động - OPEX</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>3391.848</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>3002.664</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>3195.863</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>3014.021</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>3989.84</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>3142.086</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>2868.89</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>3630.731</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <v>3610.089</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="18" t="n">
         <v>3249.136</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="18" t="n">
         <v>3948.974</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="18" t="n">
         <v>3430.902</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="18" t="n">
         <v>4740.723</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="O5" s="18" t="n">
         <v>3284.915</v>
       </c>
-      <c r="P5" s="17" t="n">
+      <c r="P5" s="18" t="n">
         <v>3830.693</v>
       </c>
-      <c r="Q5" s="17" t="n">
+      <c r="Q5" s="18" t="n">
         <v>4492.851</v>
       </c>
-      <c r="R5" s="17" t="n">
+      <c r="R5" s="18" t="n">
         <v>4823.975</v>
       </c>
-      <c r="S5" s="17" t="n">
+      <c r="S5" s="18" t="n">
         <v>3869.012</v>
       </c>
     </row>
@@ -16902,58 +16917,58 @@
           <t>LN trước dự phòng - PPOP</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>6767.163</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>7003.716</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>7738.517</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>7324.347</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>5437.482</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>6157.888</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>6456.281</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>6787.762</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <v>7407.365</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="18" t="n">
         <v>9012.630999999999</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="18" t="n">
         <v>9470.722</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="18" t="n">
         <v>8323.433000000001</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="18" t="n">
         <v>4813.876</v>
       </c>
-      <c r="O6" s="17" t="n">
+      <c r="O6" s="18" t="n">
         <v>8326.282999999999</v>
       </c>
-      <c r="P6" s="17" t="n">
+      <c r="P6" s="18" t="n">
         <v>8912.338</v>
       </c>
-      <c r="Q6" s="17" t="n">
+      <c r="Q6" s="18" t="n">
         <v>9749.272000000001</v>
       </c>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="18" t="n">
         <v>9970.798000000001</v>
       </c>
-      <c r="S6" s="17" t="n">
+      <c r="S6" s="18" t="n">
         <v>9805.262000000001</v>
       </c>
     </row>
@@ -16963,58 +16978,58 @@
           <t>Dự phòng tín dụng</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>627.184</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>218.386</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>417.381</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>609.268</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>691.259</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>534.53</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <v>807.271</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <v>944.972</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>1634.295</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="18" t="n">
         <v>1210.972</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="18" t="n">
         <v>1644.213</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <v>1109.265</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="18" t="n">
         <v>117.844</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="O7" s="18" t="n">
         <v>1090.055</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="P7" s="18" t="n">
         <v>1013.75</v>
       </c>
-      <c r="Q7" s="17" t="n">
+      <c r="Q7" s="18" t="n">
         <v>1499.256</v>
       </c>
-      <c r="R7" s="17" t="n">
+      <c r="R7" s="18" t="n">
         <v>817.564</v>
       </c>
-      <c r="S7" s="17" t="n">
+      <c r="S7" s="18" t="n">
         <v>935.292</v>
       </c>
     </row>
@@ -17024,58 +17039,58 @@
           <t>LN trước thuế - PBT</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>6139.979</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>6785.33</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>7321.136</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>6715.079</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>4746.223</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>5623.358</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="18" t="n">
         <v>5649.01</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="18" t="n">
         <v>5842.79</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <v>5773.07</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="18" t="n">
         <v>7801.659</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="18" t="n">
         <v>7826.509</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="18" t="n">
         <v>7214.168</v>
       </c>
-      <c r="N8" s="17" t="n">
+      <c r="N8" s="18" t="n">
         <v>4696.032</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="18" t="n">
         <v>7236.228</v>
       </c>
-      <c r="P8" s="17" t="n">
+      <c r="P8" s="18" t="n">
         <v>7898.588</v>
       </c>
-      <c r="Q8" s="17" t="n">
+      <c r="Q8" s="18" t="n">
         <v>8250.016</v>
       </c>
-      <c r="R8" s="17" t="n">
+      <c r="R8" s="18" t="n">
         <v>9153.234</v>
       </c>
-      <c r="S8" s="17" t="n">
+      <c r="S8" s="18" t="n">
         <v>8869.969999999999</v>
       </c>
     </row>
@@ -17085,58 +17100,58 @@
           <t>LN sau thuế - NPAT</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>4683.818</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>5614.544</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>5882.255</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>5367.54</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>3572.087</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>4537.097</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>4503.449</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <v>4668.705</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>4481.615</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="18" t="n">
         <v>6277.003</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="18" t="n">
         <v>6269.968</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>5793.022</v>
       </c>
-      <c r="N9" s="17" t="n">
+      <c r="N9" s="18" t="n">
         <v>3420.111</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="O9" s="18" t="n">
         <v>6013.511</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="P9" s="18" t="n">
         <v>6347.61</v>
       </c>
-      <c r="Q9" s="17" t="n">
+      <c r="Q9" s="18" t="n">
         <v>6613.525</v>
       </c>
-      <c r="R9" s="17" t="n">
+      <c r="R9" s="18" t="n">
         <v>6979.826</v>
       </c>
-      <c r="S9" s="17" t="n">
+      <c r="S9" s="18" t="n">
         <v>6950.28</v>
       </c>
     </row>
@@ -17146,58 +17161,58 @@
           <t>Chi phí lãi (Int Exp)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>2103.047</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>1687.071</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>1987.162</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>2123.059</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>2534.572</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>1944.138</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>2019.348</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>2255.66</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <v>2495.751</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="18" t="n">
         <v>2171.151</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="18" t="n">
         <v>2461.472</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>1946.783</v>
       </c>
-      <c r="N10" s="17" t="n">
+      <c r="N10" s="18" t="n">
         <v>1462.842</v>
       </c>
-      <c r="O10" s="17" t="n">
+      <c r="O10" s="18" t="n">
         <v>1828.132</v>
       </c>
-      <c r="P10" s="17" t="n">
+      <c r="P10" s="18" t="n">
         <v>2106.991</v>
       </c>
-      <c r="Q10" s="17" t="n">
+      <c r="Q10" s="18" t="n">
         <v>2265.937</v>
       </c>
-      <c r="R10" s="17" t="n">
+      <c r="R10" s="18" t="n">
         <v>2570.935</v>
       </c>
-      <c r="S10" s="17" t="n">
+      <c r="S10" s="18" t="n">
         <v>3148.457</v>
       </c>
     </row>
@@ -17268,30 +17283,30 @@
           <t>Thu nhập lãi thuần (NII)</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>26698.613</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>30289.775</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>27691.12</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>35507.963</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>38155.091</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="18">
         <f>'03_Income_Model'!G5</f>
         <v/>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="18">
         <f>'03_Income_Model'!H5</f>
         <v/>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="18">
         <f>'03_Income_Model'!I5</f>
         <v/>
       </c>
@@ -17302,30 +17317,30 @@
           <t>Tổng thu nhập hoạt động (TOI)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>37076.291</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>40527.191</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>40061.092</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>46990.397</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>53391.125</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="18">
         <f>SUM(G2+'03_Income_Model'!G10)</f>
         <v/>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="18">
         <f>SUM(H2+'03_Income_Model'!H10)</f>
         <v/>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="18">
         <f>SUM(I2+'03_Income_Model'!I10)</f>
         <v/>
       </c>
@@ -17336,30 +17351,30 @@
           <t>Lợi nhuận trước dự phòng (PPOP)</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>25902.896</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>27504.062</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>26809.296</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>31620.662</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>36958.691</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="18">
         <f>'03_Income_Model'!G14</f>
         <v/>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="18">
         <f>'03_Income_Model'!H14</f>
         <v/>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="18">
         <f>'03_Income_Model'!I14</f>
         <v/>
       </c>
@@ -17370,30 +17385,30 @@
           <t>LNST (NPAT)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>18415.382</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>20436.426</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>18190.866</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>21760.104</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>25954.472</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>('03_Income_Model'!G17)-MAX(('03_Income_Model'!G17)*'02_Assumptions'!G14,0)</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>('03_Income_Model'!H17)-MAX(('03_Income_Model'!H17)*'02_Assumptions'!H14,0)</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>('03_Income_Model'!I17)-MAX(('03_Income_Model'!I17)*'02_Assumptions'!I14,0)</f>
         <v/>
       </c>
@@ -17549,58 +17564,58 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>568811.4350000001</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>615270.328</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>623738.504</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>671353.524</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>699032.544</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="18" t="n">
         <v>723517.8</v>
       </c>
-      <c r="H2" s="17" t="n">
+      <c r="H2" s="18" t="n">
         <v>732470.169</v>
       </c>
-      <c r="I2" s="17" t="n">
+      <c r="I2" s="18" t="n">
         <v>781278.666</v>
       </c>
-      <c r="J2" s="17" t="n">
+      <c r="J2" s="18" t="n">
         <v>849482.012</v>
       </c>
-      <c r="K2" s="17" t="n">
+      <c r="K2" s="18" t="n">
         <v>885653.461</v>
       </c>
-      <c r="L2" s="17" t="n">
+      <c r="L2" s="18" t="n">
         <v>908306.7</v>
       </c>
-      <c r="M2" s="17" t="n">
+      <c r="M2" s="18" t="n">
         <v>927053.345</v>
       </c>
-      <c r="N2" s="17" t="n">
+      <c r="N2" s="18" t="n">
         <v>978798.549</v>
       </c>
-      <c r="O2" s="17" t="n">
+      <c r="O2" s="18" t="n">
         <v>989215.993</v>
       </c>
-      <c r="P2" s="17" t="n">
+      <c r="P2" s="18" t="n">
         <v>1037645.395</v>
       </c>
-      <c r="Q2" s="17" t="n">
+      <c r="Q2" s="18" t="n">
         <v>1129570.458</v>
       </c>
-      <c r="R2" s="17" t="n">
+      <c r="R2" s="18" t="n">
         <v>1192344.137</v>
       </c>
-      <c r="S2" s="17" t="n">
+      <c r="S2" s="18" t="n">
         <v>1190453.754</v>
       </c>
     </row>
@@ -17610,58 +17625,58 @@
           <t>Tiền mặt &amp; NHNN</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>8487.172</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>12275.92</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>8018.252</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>7734.356</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>15691.311</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="18" t="n">
         <v>18686.633</v>
       </c>
-      <c r="H3" s="17" t="n">
+      <c r="H3" s="18" t="n">
         <v>10972.959</v>
       </c>
-      <c r="I3" s="17" t="n">
+      <c r="I3" s="18" t="n">
         <v>30934.346</v>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="18" t="n">
         <v>30761.287</v>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="K3" s="18" t="n">
         <v>17252.786</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="18" t="n">
         <v>31693.359</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="18" t="n">
         <v>44223.252</v>
       </c>
-      <c r="N3" s="17" t="n">
+      <c r="N3" s="18" t="n">
         <v>57737.923</v>
       </c>
-      <c r="O3" s="17" t="n">
+      <c r="O3" s="18" t="n">
         <v>66488.939</v>
       </c>
-      <c r="P3" s="17" t="n">
+      <c r="P3" s="18" t="n">
         <v>52152.092</v>
       </c>
-      <c r="Q3" s="17" t="n">
+      <c r="Q3" s="18" t="n">
         <v>81632.149</v>
       </c>
-      <c r="R3" s="17" t="n">
+      <c r="R3" s="18" t="n">
         <v>86523.59299999999</v>
       </c>
-      <c r="S3" s="17" t="n">
+      <c r="S3" s="18" t="n">
         <v>98475.058</v>
       </c>
     </row>
@@ -17671,58 +17686,58 @@
           <t>TG các TCTD khác</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>70584.15399999999</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>72530.371</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>72130.842</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>72296.806</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>82873.754</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="18" t="n">
         <v>66839.068</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="18" t="n">
         <v>71193.28200000001</v>
       </c>
-      <c r="I4" s="17" t="n">
+      <c r="I4" s="18" t="n">
         <v>69386.02099999999</v>
       </c>
-      <c r="J4" s="17" t="n">
+      <c r="J4" s="18" t="n">
         <v>104072.32</v>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="K4" s="18" t="n">
         <v>89074.53999999999</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="18" t="n">
         <v>88903.726</v>
       </c>
-      <c r="M4" s="17" t="n">
+      <c r="M4" s="18" t="n">
         <v>90014.29300000001</v>
       </c>
-      <c r="N4" s="17" t="n">
+      <c r="N4" s="18" t="n">
         <v>84590.474</v>
       </c>
-      <c r="O4" s="17" t="n">
+      <c r="O4" s="18" t="n">
         <v>81883.42999999999</v>
       </c>
-      <c r="P4" s="17" t="n">
+      <c r="P4" s="18" t="n">
         <v>80845.693</v>
       </c>
-      <c r="Q4" s="17" t="n">
+      <c r="Q4" s="18" t="n">
         <v>92999.08900000001</v>
       </c>
-      <c r="R4" s="17" t="n">
+      <c r="R4" s="18" t="n">
         <v>114958.312</v>
       </c>
-      <c r="S4" s="17" t="n">
+      <c r="S4" s="18" t="n">
         <v>87777.341</v>
       </c>
     </row>
@@ -17732,58 +17747,58 @@
           <t>Cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>343605.581</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>361815.215</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>387775.129</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>406148.421</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>415752.256</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="18" t="n">
         <v>460145.233</v>
       </c>
-      <c r="H5" s="17" t="n">
+      <c r="H5" s="18" t="n">
         <v>460753.044</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="I5" s="18" t="n">
         <v>469588.515</v>
       </c>
-      <c r="J5" s="17" t="n">
+      <c r="J5" s="18" t="n">
         <v>512513.672</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="K5" s="18" t="n">
         <v>552577.121</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="18" t="n">
         <v>584713.478</v>
       </c>
-      <c r="M5" s="17" t="n">
+      <c r="M5" s="18" t="n">
         <v>617924.5699999999</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="18" t="n">
         <v>623634.2709999999</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="O5" s="18" t="n">
         <v>655007.208</v>
       </c>
-      <c r="P5" s="17" t="n">
+      <c r="P5" s="18" t="n">
         <v>700801.926</v>
       </c>
-      <c r="Q5" s="17" t="n">
+      <c r="Q5" s="18" t="n">
         <v>756078.003</v>
       </c>
-      <c r="R5" s="17" t="n">
+      <c r="R5" s="18" t="n">
         <v>757118.751</v>
       </c>
-      <c r="S5" s="17" t="n">
+      <c r="S5" s="18" t="n">
         <v>785612.53</v>
       </c>
     </row>
@@ -17793,58 +17808,58 @@
           <t>CK đầu tư</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>97586.088</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>120301.385</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>97227.579</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>103225.63</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>103651.92</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="18" t="n">
         <v>99071.125</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <v>107847.625</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <v>121243.204</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="18" t="n">
         <v>104993.945</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="18" t="n">
         <v>131188.842</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="18" t="n">
         <v>113677.245</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="18" t="n">
         <v>102135.236</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="18" t="n">
         <v>148623.636</v>
       </c>
-      <c r="O6" s="17" t="n">
+      <c r="O6" s="18" t="n">
         <v>124378.656</v>
       </c>
-      <c r="P6" s="17" t="n">
+      <c r="P6" s="18" t="n">
         <v>146985.597</v>
       </c>
-      <c r="Q6" s="17" t="n">
+      <c r="Q6" s="18" t="n">
         <v>139296.462</v>
       </c>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="18" t="n">
         <v>145526.404</v>
       </c>
-      <c r="S6" s="17" t="n">
+      <c r="S6" s="18" t="n">
         <v>141063.971</v>
       </c>
     </row>
@@ -17854,58 +17869,58 @@
           <t>Tiền gửi khách hàng</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>314752.525</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>328914.024</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>321633.599</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>318918.817</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>358403.785</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="18" t="n">
         <v>387297.891</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <v>381946.519</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <v>409044.572</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="18" t="n">
         <v>454660.779</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="18" t="n">
         <v>458040.69</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="18" t="n">
         <v>481860.239</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="18" t="n">
         <v>494954.017</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="18" t="n">
         <v>533392.35</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="O7" s="18" t="n">
         <v>531583.052</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="P7" s="18" t="n">
         <v>545078.843</v>
       </c>
-      <c r="Q7" s="17" t="n">
+      <c r="Q7" s="18" t="n">
         <v>595086.941</v>
       </c>
-      <c r="R7" s="17" t="n">
+      <c r="R7" s="18" t="n">
         <v>618911.535</v>
       </c>
-      <c r="S7" s="17" t="n">
+      <c r="S7" s="18" t="n">
         <v>599808.238</v>
       </c>
     </row>
@@ -17915,58 +17930,58 @@
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>93055.837</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>98585.99000000001</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>104475.159</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>109899.149</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>113424.966</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="18" t="n">
         <v>117965.416</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="18" t="n">
         <v>122464.97</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="18" t="n">
         <v>127129.786</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="18" t="n">
         <v>131628.065</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="18" t="n">
         <v>137872.726</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="18" t="n">
         <v>138551.657</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="18" t="n">
         <v>144367.982</v>
       </c>
-      <c r="N8" s="17" t="n">
+      <c r="N8" s="18" t="n">
         <v>147939.621</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="18" t="n">
         <v>153952.665</v>
       </c>
-      <c r="P8" s="17" t="n">
+      <c r="P8" s="18" t="n">
         <v>161827.229</v>
       </c>
-      <c r="Q8" s="17" t="n">
+      <c r="Q8" s="18" t="n">
         <v>179430.593</v>
       </c>
-      <c r="R8" s="17" t="n">
+      <c r="R8" s="18" t="n">
         <v>179501.442</v>
       </c>
-      <c r="S8" s="17" t="n">
+      <c r="S8" s="18" t="n">
         <v>186682.773</v>
       </c>
     </row>
@@ -17976,58 +17991,58 @@
           <t>TPDN (trái phiếu TCKT)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>62608.793</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>76582.978</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>49345.086</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>43501.086</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>41014.822</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="18" t="n">
         <v>37794.098</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>39787.78</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <v>48291.891</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>42428.655</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="18" t="n">
         <v>41954.418</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="18" t="n">
         <v>41361.915</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="18" t="n">
         <v>27812.245</v>
       </c>
-      <c r="N9" s="17" t="n">
+      <c r="N9" s="18" t="n">
         <v>45822.964</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="O9" s="18" t="n">
         <v>42017.148</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="P9" s="18" t="n">
         <v>43084.677</v>
       </c>
-      <c r="Q9" s="17" t="n">
+      <c r="Q9" s="18" t="n">
         <v>38179.178</v>
       </c>
-      <c r="R9" s="17" t="n">
+      <c r="R9" s="18" t="n">
         <v>56486.424</v>
       </c>
-      <c r="S9" s="17" t="n">
+      <c r="S9" s="18" t="n">
         <v>56648.503</v>
       </c>
     </row>
@@ -18037,58 +18052,58 @@
           <t>Giấy tờ có giá (Bonds)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>33679.824</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>32730.686</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>37122.383</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>42858.083</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>34006.619</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="18" t="n">
         <v>46729.093</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <v>54957.735</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <v>61825.221</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="18" t="n">
         <v>84703.3</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="18" t="n">
         <v>93776.798</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="18" t="n">
         <v>111985.283</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="18" t="n">
         <v>126061.309</v>
       </c>
-      <c r="N10" s="17" t="n">
+      <c r="N10" s="18" t="n">
         <v>140422.321</v>
       </c>
-      <c r="O10" s="17" t="n">
+      <c r="O10" s="18" t="n">
         <v>147933.07</v>
       </c>
-      <c r="P10" s="17" t="n">
+      <c r="P10" s="18" t="n">
         <v>172337.642</v>
       </c>
-      <c r="Q10" s="17" t="n">
+      <c r="Q10" s="18" t="n">
         <v>181742.521</v>
       </c>
-      <c r="R10" s="17" t="n">
+      <c r="R10" s="18" t="n">
         <v>215330.128</v>
       </c>
-      <c r="S10" s="17" t="n">
+      <c r="S10" s="18" t="n">
         <v>217897.008</v>
       </c>
     </row>
@@ -18098,58 +18113,58 @@
           <t>Tiền gửi Kho bạc NN</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <v>34725.067</v>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>36043.585</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <v>49271.129</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="18" t="n">
         <v>71800.99099999999</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="18" t="n">
         <v>70525.05100000001</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="18" t="n">
         <v>70425.788</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <v>68014.89599999999</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <v>72030.916</v>
       </c>
-      <c r="J11" s="17" t="n">
+      <c r="J11" s="18" t="n">
         <v>80543.55499999999</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="K11" s="18" t="n">
         <v>74415.311</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="18" t="n">
         <v>72421.614</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="18" t="n">
         <v>51868.38</v>
       </c>
-      <c r="N11" s="17" t="n">
+      <c r="N11" s="18" t="n">
         <v>39512.096</v>
       </c>
-      <c r="O11" s="17" t="n">
+      <c r="O11" s="18" t="n">
         <v>44019.699</v>
       </c>
-      <c r="P11" s="17" t="n">
+      <c r="P11" s="18" t="n">
         <v>37474.422</v>
       </c>
-      <c r="Q11" s="17" t="n">
+      <c r="Q11" s="18" t="n">
         <v>41323.67</v>
       </c>
-      <c r="R11" s="17" t="n">
+      <c r="R11" s="18" t="n">
         <v>72324.96400000001</v>
       </c>
-      <c r="S11" s="17" t="n">
+      <c r="S11" s="18" t="n">
         <v>66877.443</v>
       </c>
     </row>
@@ -18159,58 +18174,58 @@
           <t>Tiền gửi ký quỹ (trừ đi)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>11956.065</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>11666.416</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>12211.189</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>13080.351</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>13303.703</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>11717.799</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="18" t="n">
         <v>11677.037</v>
       </c>
-      <c r="I12" s="17" t="n">
+      <c r="I12" s="18" t="n">
         <v>11139.678</v>
       </c>
-      <c r="J12" s="17" t="n">
+      <c r="J12" s="18" t="n">
         <v>13948.273</v>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="K12" s="18" t="n">
         <v>12662.231</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="18" t="n">
         <v>15116.796</v>
       </c>
-      <c r="M12" s="17" t="n">
+      <c r="M12" s="18" t="n">
         <v>15930.792</v>
       </c>
-      <c r="N12" s="17" t="n">
+      <c r="N12" s="18" t="n">
         <v>20192.422</v>
       </c>
-      <c r="O12" s="17" t="n">
+      <c r="O12" s="18" t="n">
         <v>16556.034</v>
       </c>
-      <c r="P12" s="17" t="n">
+      <c r="P12" s="18" t="n">
         <v>15468.904</v>
       </c>
-      <c r="Q12" s="17" t="n">
+      <c r="Q12" s="18" t="n">
         <v>18977.789</v>
       </c>
-      <c r="R12" s="17" t="n">
+      <c r="R12" s="18" t="n">
         <v>23104.566</v>
       </c>
-      <c r="S12" s="17" t="n">
+      <c r="S12" s="18" t="n">
         <v>23741.27</v>
       </c>
     </row>
@@ -18220,58 +18235,58 @@
           <t>Vốn chuyên dùng (trừ đi)</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="17" t="n">
+      <c r="J13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="K13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="17" t="n">
+      <c r="L13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="17" t="n">
+      <c r="M13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="17" t="n">
+      <c r="N13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="17" t="n">
+      <c r="O13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="17" t="n">
+      <c r="P13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="17" t="n">
+      <c r="Q13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="17" t="n">
+      <c r="R13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="17" t="n">
+      <c r="S13" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18281,58 +18296,58 @@
           <t>Tài sản sinh lãi (IEA)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>520262.995</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>566922.8910000001</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>565151.802</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>589405.213</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>617969.241</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>644742.059</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <v>650766.91</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="18" t="n">
         <v>691152.086</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="18" t="n">
         <v>752341.2240000002</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="18" t="n">
         <v>790093.2890000001</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="18" t="n">
         <v>818987.808</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="18" t="n">
         <v>854297.351</v>
       </c>
-      <c r="N14" s="17" t="n">
+      <c r="N14" s="18" t="n">
         <v>914586.304</v>
       </c>
-      <c r="O14" s="17" t="n">
+      <c r="O14" s="18" t="n">
         <v>927758.233</v>
       </c>
-      <c r="P14" s="17" t="n">
+      <c r="P14" s="18" t="n">
         <v>980785.308</v>
       </c>
-      <c r="Q14" s="17" t="n">
+      <c r="Q14" s="18" t="n">
         <v>1070005.703</v>
       </c>
-      <c r="R14" s="17" t="n">
+      <c r="R14" s="18" t="n">
         <v>1104127.06</v>
       </c>
-      <c r="S14" s="17" t="n">
+      <c r="S14" s="18" t="n">
         <v>1112928.9</v>
       </c>
     </row>
@@ -18342,75 +18357,75 @@
           <t>Tổng tín dụng (tỷ)</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="18">
         <f>B5+B9</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="18">
         <f>C5+C9</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <f>D5+D9</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="18">
         <f>E5+E9</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="18">
         <f>F5+F9</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="18">
         <f>G5+G9</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="18">
         <f>H5+H9</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="18">
         <f>I5+I9</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="18">
         <f>J5+J9</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="18">
         <f>K5+K9</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="18">
         <f>L5+L9</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="18">
         <f>M5+M9</f>
         <v/>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="18">
         <f>N5+N9</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="18">
         <f>O5+O9</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="18">
         <f>P5+P9</f>
         <v/>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="18">
         <f>Q5+Q9</f>
         <v/>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="18">
         <f>R5+R9</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="18">
         <f>S5+S9</f>
         <v/>
       </c>
@@ -18421,75 +18436,75 @@
           <t>Tổng huy động (tỷ)</t>
         </is>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="18">
         <f>B7+B10+B17+B11*0.0-B12-B13</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="18">
         <f>C7+C10+C17+C11*0.0-C12-C13</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="18">
         <f>D7+D10+D17+D11*0.0-D12-D13</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="18">
         <f>E7+E10+E17+E11*0.0-E12-E13</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="18">
         <f>F7+F10+F17+F11*0.0-F12-F13</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="18">
         <f>G7+G10+G17+G11*0.5-G12-G13</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="18">
         <f>H7+H10+H17+H11*0.5-H12-H13</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="18">
         <f>I7+I10+I17+I11*0.5-I12-I13</f>
         <v/>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="18">
         <f>J7+J10+J17+J11*0.5-J12-J13</f>
         <v/>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="18">
         <f>K7+K10+K17+K11*0.4-K12-K13</f>
         <v/>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="18">
         <f>L7+L10+L17+L11*0.4-L12-L13</f>
         <v/>
       </c>
-      <c r="M16" s="17">
+      <c r="M16" s="18">
         <f>M7+M10+M17+M11*0.4-M12-M13</f>
         <v/>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="18">
         <f>N7+N10+N17+N11*0.4-N12-N13</f>
         <v/>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="18">
         <f>O7+O10+O17+O11*0.2-O12-O13</f>
         <v/>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="18">
         <f>P7+P10+P17+P11*0.2-P12-P13</f>
         <v/>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16" s="18">
         <f>Q7+Q10+Q17+Q11*0.2-Q12-Q13</f>
         <v/>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="18">
         <f>R7+R10+R17+R11*0.2-R12-R13</f>
         <v/>
       </c>
-      <c r="S16" s="17">
+      <c r="S16" s="18">
         <f>S7+S10+S17+S11*0.2-S12-S13</f>
         <v/>
       </c>
@@ -18500,58 +18515,58 @@
           <t>Tiền gửi của TCTD khác</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <v>45606.142</v>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>60349.404</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>57307.332</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E17" s="18" t="n">
         <v>68284.02899999999</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>61293.738</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>47939.774</v>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <v>49594.4</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="18" t="n">
         <v>57582.142</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="18" t="n">
         <v>50619.678</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="18" t="n">
         <v>76496.75599999999</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="18" t="n">
         <v>60471.427</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="18" t="n">
         <v>70584.329</v>
       </c>
-      <c r="N17" s="17" t="n">
+      <c r="N17" s="18" t="n">
         <v>72210.834</v>
       </c>
-      <c r="O17" s="17" t="n">
+      <c r="O17" s="18" t="n">
         <v>81331.394</v>
       </c>
-      <c r="P17" s="17" t="n">
+      <c r="P17" s="18" t="n">
         <v>91640.53599999999</v>
       </c>
-      <c r="Q17" s="17" t="n">
+      <c r="Q17" s="18" t="n">
         <v>93471.217</v>
       </c>
-      <c r="R17" s="17" t="n">
+      <c r="R17" s="18" t="n">
         <v>83014.31299999999</v>
       </c>
-      <c r="S17" s="17" t="n">
+      <c r="S17" s="18" t="n">
         <v>86820.944</v>
       </c>
     </row>
@@ -18622,19 +18637,19 @@
           <t>Tổng tài sản</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <v>568728.95</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <v>699032.544</v>
       </c>
-      <c r="D2" s="17" t="n">
+      <c r="D2" s="18" t="n">
         <v>849482.012</v>
       </c>
-      <c r="E2" s="17" t="n">
+      <c r="E2" s="18" t="n">
         <v>978798.549</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>1192344.137</v>
       </c>
       <c r="G2" s="14">
@@ -18656,30 +18671,30 @@
           <t>Cho vay khách hàng (Gross)</t>
         </is>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <v>343605.581</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <v>415752.256</v>
       </c>
-      <c r="D3" s="17" t="n">
+      <c r="D3" s="18" t="n">
         <v>512513.672</v>
       </c>
-      <c r="E3" s="17" t="n">
+      <c r="E3" s="18" t="n">
         <v>623634.2709999999</v>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="18" t="n">
         <v>757118.751</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="18">
         <f>F3*(1+'02_Assumptions'!G4)</f>
         <v/>
       </c>
-      <c r="H3" s="17">
+      <c r="H3" s="18">
         <f>G3*(1+'02_Assumptions'!H4)</f>
         <v/>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="18">
         <f>H3*(1+'02_Assumptions'!I4)</f>
         <v/>
       </c>
@@ -18690,19 +18705,19 @@
           <t>Trái phiếu doanh nghiệp</t>
         </is>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <v>62608.793</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <v>41014.822</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="18" t="n">
         <v>42428.655</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="18" t="n">
         <v>45822.964</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>56486.424</v>
       </c>
       <c r="G4" s="14">
@@ -18724,30 +18739,30 @@
           <t>Tiền gửi khách hàng</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <v>314752.525</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>358403.785</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="18" t="n">
         <v>454660.779</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="18" t="n">
         <v>533392.35</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="18" t="n">
         <v>618911.535</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>F5*(1+'02_Assumptions'!G5)</f>
         <v/>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="18">
         <f>G5*(1+'02_Assumptions'!H5)</f>
         <v/>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="18">
         <f>H5*(1+'02_Assumptions'!I5)</f>
         <v/>
       </c>
@@ -18758,19 +18773,19 @@
           <t>Giấy tờ có giá phát hành (Bonds)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <v>33679.824</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="18" t="n">
         <v>34006.619</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>84703.3</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>140422.321</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>215330.128</v>
       </c>
       <c r="G6" s="14">
@@ -18792,19 +18807,19 @@
           <t>Tiền gửi Kho bạc Nhà nước</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <v>34711.477</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="18" t="n">
         <v>70525.05100000001</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <v>80543.55499999999</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="18" t="n">
         <v>39512.09600000001</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="18" t="n">
         <v>72324.96399999999</v>
       </c>
       <c r="G7" s="14">
@@ -18826,19 +18841,19 @@
           <t>Tiền gửi ký quỹ (trừ đi)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <v>11956.065</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="18" t="n">
         <v>13303.703</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <v>13948.273</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="18" t="n">
         <v>20192.422</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>23104.566</v>
       </c>
       <c r="G8" s="14">
@@ -18860,19 +18875,19 @@
           <t>Vốn chuyên dùng (trừ đi)</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="18" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="14">
@@ -18894,19 +18909,19 @@
           <t>Vốn chủ sở hữu (VCSH)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>93041.47199999999</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>113424.966</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>131616.065</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="18" t="n">
         <v>147939.621</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>179501.442</v>
       </c>
       <c r="G10" s="14">
@@ -18928,35 +18943,35 @@
           <t>Tổng tín dụng (tỷ)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="18">
         <f>B3+B4</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <f>C3+C4</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>D3+D4</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <f>E3+E4</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>F3+F4</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>G3+G4</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="18">
         <f>H3+H4</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="18">
         <f>I3+I4</f>
         <v/>
       </c>
@@ -18967,35 +18982,35 @@
           <t>Tổng huy động (tỷ)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="18">
         <f>B5+B6+B13+B7*0.0-B8-B9</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <f>C5+C6+C13+C7*0.0-C8-C9</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>D5+D6+D13+D7*0.5-D8-D9</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <f>E5+E6+E13+E7*0.4-E8-E9</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>F5+F6+F13+F7*0.2-F8-F9</f>
         <v/>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="18">
         <f>G5+G6+G13+G7*0.2-G8-G9</f>
         <v/>
       </c>
-      <c r="H12" s="17">
+      <c r="H12" s="18">
         <f>H5+H6+H13+H7*0.2-H8-H9</f>
         <v/>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="18">
         <f>I5+I6+I13+I7*0.2-I8-I9</f>
         <v/>
       </c>
@@ -19006,30 +19021,30 @@
           <t>Tiền gửi của TCTD khác</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <v>45606.142</v>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>61293.738</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>50619.678</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>72210.834</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="18" t="n">
         <v>83014.31299999999</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="18">
         <f>F13*(1+'02_Assumptions'!G5)</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="18">
         <f>G13*(1+'02_Assumptions'!H5)</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="18">
         <f>H13*(1+'02_Assumptions'!I5)</f>
         <v/>
       </c>
